--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>5442</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -775,11 +770,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>5442</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -770,6 +775,11 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>90960</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122496578</v>
       </c>
       <c r="B2" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 34020-2021 artfynd.xlsx
+++ b/artfynd/A 34020-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122496578</v>
+        <v>114415257</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,22 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SKOMAKARTORP, Upl</t>
+          <t>Skomakartorp, Skomakartorp, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637337</v>
+        <v>637296</v>
       </c>
       <c r="R2" t="n">
-        <v>6636103</v>
+        <v>6636058</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,37 +755,147 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn, Margaux Boeraeve</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122496578</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SKOMAKARTORP, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>637337</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6636103</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Åke Berg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Åke Berg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
